--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_947_Morocco_Mediterranean.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_947_Morocco_Mediterranean.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R13bf9e6f6bed4496"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Raac9f6e548df4e41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R0d0c53cf3e3b45b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rd584661ab460488a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Ra4503d529b1a4c97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rc57c34cae69b4c29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Ra9263c4345944174"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rfcb4ae2c7bee478e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rfafa357ab81349ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R986001fe517f4757"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R64b4495090da4446"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R119f9ee4f1e144f3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ947CommercialTable" displayName="EEZ947CommercialTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ947CommercialTable" displayName="EEZ947CommercialTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ947FunctionalTable" displayName="EEZ947FunctionalTable" ref="A1:O21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O21"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ947FunctionalTable" displayName="EEZ947FunctionalTable" ref="A1:E21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E21"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ947ValidationTable" displayName="EEZ947ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ947ValidationTable" displayName="EEZ947ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -8064,7 +8018,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra172decec0f74a6d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b28ecea631b4e97"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8074,20 +8028,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -8095,714 +8039,250 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>800.0397543518</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>800.0397543518</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$111,A2,'Species'!$U$2:$U$111))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>103065.08548803911</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>103065.08548803911</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1076.512529344</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.252654809522854</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1789.1831914467416</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1076.512529344</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1901.353836884635</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$111,A3,'Species'!$U$2:$U$111))</x:f>
-        <x:v>2046831.2281225978</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.252654809522854</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1789.1831914467416</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1926078.1228841022</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>120753.10523849563</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0626937733230053</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.0626937733230054</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>665.2421180217</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.3646079525313803</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>231.53036292606492</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>665.2421180217</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>243.58163628743065</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$111,A4,'Species'!$U$2:$U$111))</x:f>
-        <x:v>162040.76363504175</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.3646079525313803</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>231.53036292606492</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>154023.74901926832</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>8017.014615773427</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0520505095274009</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.052050509527400875</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>797.1357977371</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.2167378912034654</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>164.716797979846</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>797.1357977371</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>218.55569015321808</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$111,A5,'Species'!$U$2:$U$111))</x:f>
-        <x:v>174218.56442026794</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.2167378912034654</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>164.716797979846</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>131301.65615836528</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>42916.90826190266</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.3268573262331116</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.3268573262331117</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>6967.7568767863</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.0138721594143147</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>103.24574429017753</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>6967.7568767863</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>105.9188928544639</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$111,A6,'Species'!$U$2:$U$111))</x:f>
-        <x:v>738017.0940682822</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.0138721594143147</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>103.24574429017753</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>719391.2447768043</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>18625.849291477818</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0258911259022294</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.025891125902229466</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>1777.0575928942003</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.1091266717918487</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>12.856615974961075</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>1777.0575928942003</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>13.247194903913401</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$111,A7,'Species'!$U$2:$U$111))</x:f>
-        <x:v>23541.028288548667</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.1091266717918487</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>12.856615974961075</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>22846.94703722945</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>694.0812513192177</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0303796060886472</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.03037960608864728</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>12790.887674209202</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.632251889672051</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>428.7971495218873</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>12790.887674209202</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>578.8996304948911</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$111,A8,'Species'!$U$2:$U$111))</x:f>
-        <x:v>7404640.148301363</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.632251889672051</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>428.7971495218873</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>5484696.1745555485</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>1919943.9737458145</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.3500547546558306</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.35005475465583047</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>26919.162983113107</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.6005649934906194</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>398.6254233572895</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>26919.162983113107</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>566.6403370965302</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$111,A9,'Species'!$U$2:$U$111))</x:f>
-        <x:v>15253483.58710765</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.6005649934906194</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>398.6254233572895</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>10730662.740567338</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>4522820.846540311</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.4214856953281887</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.4214856953281887</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>1.55</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.3499999999999996</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>223.87211385683378</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>1.55</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>223.872113856834</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$111,A10,'Species'!$U$2:$U$111))</x:f>
-        <x:v>347.0017764780927</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.3499999999999996</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>223.87211385683378</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>347.0017764780924</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>3.410605131648481e-13</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0000000000000009</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>9.828782913633891e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>810.2171982534999</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.9568473752862428</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>905.4143539549044</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>810.2171982534999</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>912.9127480273153</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$111,A11,'Species'!$U$2:$U$111))</x:f>
-        <x:v>739657.6089565947</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.9568473752862428</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>905.4143539549044</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>733582.2811198453</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>6075.327836749377</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0082817265262667</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.008281726526266589</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>5789.6333288962005</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.378919430102597</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2392.8717919357887</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>5789.6333288962005</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2600.382342767856</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$111,A12,'Species'!$U$2:$U$111))</x:f>
-        <x:v>15055260.279561961</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.378919430102597</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2392.8717919357887</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>13853850.278367016</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>1201410.0011949446</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0867202963114855</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.08672029631148558</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>7650.9523012972995</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.469764515726471</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2949.609448148902</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>7650.9523012972995</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2988.280161459376</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$H$2:$H$111,A13,'Species'!$U$2:$U$111))</x:f>
-        <x:v>22863188.97823868</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.469764515726471</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2949.609448148902</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>22567321.1952431</x:v>
       </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>295867.7829955779</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0131104520751866</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.013110452075186619</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b1d1a9639d04a27"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8a9bde1d54949e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8812,20 +8292,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -8833,1146 +8303,402 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>5002.4205563041</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.784595378506421</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>608.9692711584737</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>5002.4205563041</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>611.6739762864576</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$111,A2,'Species'!$U$2:$U$111))</x:f>
-        <x:v>3059850.4727316415</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.784595378506421</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>608.9692711584737</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>3046320.4002006743</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>13530.072530967183</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0044414476330448</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.004441447633044738</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>0.0427160106</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.34</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2187.761623949552</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>0.0427160106</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$111,A3,'Species'!$U$2:$U$111))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>93.45244871890228</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.34</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>93.45244871890228</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1440.6777835442</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.386991975288893</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2437.7657739400743</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1440.6777835442</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2599.8543481739853</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$111,A4,'Species'!$U$2:$U$111))</x:f>
-        <x:v>3745552.3998650485</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.386991975288893</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2437.7657739400743</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>3512034.9919998976</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>233517.40786515083</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0664906267725358</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.06649062677253577</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>3530.9922535194</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.9459892825564036</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>883.0581081954531</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>3530.9922535194</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1109.730678665458</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$111,A5,'Species'!$U$2:$U$111))</x:f>
-        <x:v>3918450.429860559</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.9459892825564036</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>883.0581081954531</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>3118071.3394456413</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>800379.0904149176</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.2566904356194801</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.25669043561948013</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>6.8</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.36</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2290.867652767775</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>6.8</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$111,A6,'Species'!$U$2:$U$111))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>15577.900038820868</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.36</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>15577.900038820868</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>5130.719012988099</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.228991398872019</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>1694.3042447090832</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>5130.719012988099</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2210.5211100921865</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$111,A7,'Species'!$U$2:$U$111))</x:f>
-        <x:v>11341562.68816154</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.228991398872019</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>1694.3042447090832</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>8692999.002115333</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>2648563.6860462073</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.3046777855837453</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.3046777855837453</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>265.19314035360003</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.378815426162226</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>239.22988205794755</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>265.19314035360003</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>240.12740109820268</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$111,A8,'Species'!$U$2:$U$111))</x:f>
-        <x:v>63680.13958218088</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.378815426162226</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>239.22988205794755</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>63442.12368936847</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>238.0158928124074</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0037517012194894</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.0037517012194895004</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>92.7601391427</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.92041485010447</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>832.5586744651193</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>92.7601391427</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>836.4910887547809</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$111,A9,'Species'!$U$2:$U$111))</x:f>
-        <x:v>77593.02978452209</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.92041485010447</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>832.5586744651193</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>77228.25848784634</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>364.77129667575355</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0047232878717984</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.004723287871798362</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>5524.4401885426005</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.42692804499089</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>2672.563574881154</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>5524.4401885426005</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>2713.683129572392</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$111,A10,'Species'!$U$2:$U$111))</x:f>
-        <x:v>14991580.13997978</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.42692804499089</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>2672.563574881154</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>14764417.61950853</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>227162.52047125064</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0153858097437651</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.015385809743765045</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>634.7137377731</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.3707417059692015</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>234.82358063354917</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>634.7137377731</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>246.36987302493318</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$111,A11,'Species'!$U$2:$U$111))</x:f>
-        <x:v>156374.34298233938</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.3707417059692015</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>234.82358063354917</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>149045.75258118293</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>7328.590401156456</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0491700721036292</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.049170072103629295</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>229.4570759657</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.452501865576561</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2834.665810192243</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>229.4570759657</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2866.0619241279414</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$111,A12,'Species'!$U$2:$U$111))</x:f>
-        <x:v>657638.1886470254</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.452501865576561</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2834.665810192243</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>650434.128146654</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>7204.060500371386</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0110757726088246</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.011075772608824547</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>0.0065826417</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.08</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>1202.2644346174131</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>0.0065826417</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$111,A13,'Species'!$U$2:$U$111))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>7.914076001739507</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.08</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>7.914076001739507</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>9683.3474795943</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.60739616090297</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>404.9451118497403</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>9683.3474795943</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>492.3911452287412</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$111,A14,'Species'!$U$2:$U$111))</x:f>
-        <x:v>4767994.555125282</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.60739616090297</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>404.9451118497403</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>3921224.2282042145</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>846770.3269210677</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.215945398080145</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.2159453980801448</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>10557.355763799802</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.362547141912846</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>230.43430949273193</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>10557.355763799802</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>328.89747367010136</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$111,A15,'Species'!$U$2:$U$111))</x:f>
-        <x:v>3472287.6393502383</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.362547141912846</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>230.43430949273193</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>2432776.985500321</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>1039510.6538499175</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.4272938539149052</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.42729385391490515</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>12724.396234861</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.9634169303616744</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>919.2146352902207</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>12724.396234861</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>1351.9541552298322</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$111,A16,'Species'!$U$2:$U$111))</x:f>
-        <x:v>17202800.36251116</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.9634169303616744</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>919.2146352902207</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>11696451.244316012</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>5506349.11819515</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.4707709204423014</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.4707709204423014</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>857.1070878455001</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>2.6119427872535628</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>40.92067484207804</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>857.1070878455001</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>75.04012141970172</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$111,A17,'Species'!$U$2:$U$111))</x:f>
-        <x:v>64317.419941613276</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>2.6119427872535628</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>40.92067484207804</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>35073.400446566135</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>29244.01949504714</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.8337948166617042</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.8337948166617041</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>1777.0575928942003</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.1091266717918487</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>12.856615974961075</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>1777.0575928942003</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>13.247194903913401</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$111,A18,'Species'!$U$2:$U$111))</x:f>
-        <x:v>23541.028288548667</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.1091266717918487</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>12.856615974961075</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>22846.94703722945</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>694.0812513192177</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0303796060886472</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.03037960608864728</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>30.528380248599998</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.2370814496709475</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>172.61615942626915</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>30.528380248599998</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>185.61157213580637</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$111,A19,'Species'!$U$2:$U$111))</x:f>
-        <x:v>5666.420652702345</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.2370814496709475</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>172.61615942626915</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>5269.691752018103</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>396.72890068424203</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.0752850298183587</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.07528502981835875</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>7767.796631138101</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.023772791166214</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>105.62647610584578</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>7767.796631138101</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>108.27808959167999</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$111,A20,'Species'!$U$2:$U$111))</x:f>
-        <x:v>841082.1795563212</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.023772791166214</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>105.62647610584578</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>820484.9852539779</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>20597.194302343298</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.025103682178861</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.025103682178860977</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>790.3357977371</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.206901335195151</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>161.02797636466443</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>790.3357977371</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>200.72564704226878</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$111,A21,'Species'!$U$2:$U$111))</x:f>
-        <x:v>158640.66438144707</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.206901335195151</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>161.02797636466443</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>127266.17415815796</x:v>
       </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>31374.490223289118</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.2465265450998706</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.24652654509987063</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G21">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O21">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb71c9a67f9a4981"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4230314697a44439"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10147,7 +8873,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -10246,7 +8972,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>64564291.36796549</x:v>
+        <x:v>56427166.47699314</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10260,7 +8986,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>64564291.36796549</x:v>
+        <x:v>53151066.53940716</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10274,7 +9000,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-8137124.890972346</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10288,7 +9014,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-11413224.828558333</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10299,9 +9025,9 @@
         <x:v>EEZ_947</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -10313,47 +9039,19 @@
         <x:v>EEZ_947</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_947</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_947</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4cc54f04352f4787"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5a19bf28fc042de"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10400,7 +9098,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
